--- a/vse-loti/341406920/spec-341406920.xlsx
+++ b/vse-loti/341406920/spec-341406920.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -465,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2379,8 +2382,15 @@
         <v>137743586.76</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>НДС 22 %, ставка из документа: "ь ответственного хранения за 1 м2 составляет 19,48 руб., в том числе НДС 22 % 3,51 руб." — Проект_договора_560.26.00747_конкурентная_без_обеспечения_не_МСП.txt; суммы источника указаны без НДС: "Цена за единицу (предложение участника) без НДС" — 226220_297.26.00332_КОММ.txt. «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>Источник: 226220_297.26.00332_КОММ.xlsx
 226220_190.26.00536_КОММ.xlsx
@@ -2391,11 +2401,11 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60"/>
+    <row r="61"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A58:B60"/>
+    <mergeCell ref="A59:B61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341406920/spec-341406920.xlsx
+++ b/vse-loti/341406920/spec-341406920.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -480,6 +480,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -515,17 +516,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -555,13 +561,16 @@
         <v>2.99</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>112220</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>335537.8</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>112220</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>136908.4</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>409356.12</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +599,16 @@
         <v>20.5</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>112220</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>2300510</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>112220</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>136908.4</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>2806622.2</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +637,16 @@
         <v>9</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>112220</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>1009980</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>112220</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>136908.4</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1232175.6</v>
       </c>
     </row>
     <row r="5">
@@ -660,13 +675,16 @@
         <v>4.29</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>110490</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>474002.1</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>110490</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>134797.8</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>578282.5600000001</v>
       </c>
     </row>
     <row r="6">
@@ -695,13 +713,16 @@
         <v>52.402</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>101100</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>5297842.2</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>101100</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>123342</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6463367.48</v>
       </c>
     </row>
     <row r="7">
@@ -730,13 +751,16 @@
         <v>21.4635</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>101100</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>2169963.89</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>101100</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>123342</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>2647355.95</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +789,16 @@
         <v>30</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>101100</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>3033000</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>101100</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>123342</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>3700260</v>
       </c>
     </row>
     <row r="9">
@@ -800,13 +827,16 @@
         <v>28.5149</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>102280</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>2916503.97</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>102280</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>124781.6</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>3558134.84</v>
       </c>
     </row>
     <row r="10">
@@ -835,13 +865,16 @@
         <v>15.702</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>102280</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>1606000.56</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>102280</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>124781.6</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1959320.68</v>
       </c>
     </row>
     <row r="11">
@@ -870,13 +903,16 @@
         <v>25</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>102280</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>2557000</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>102280</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>124781.6</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>3119540</v>
       </c>
     </row>
     <row r="12">
@@ -905,13 +941,16 @@
         <v>5.5</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>109840</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>604120</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>109840</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>134004.8</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>737026.4</v>
       </c>
     </row>
     <row r="13">
@@ -940,13 +979,16 @@
         <v>19.4559</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>109840</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>2137039.35</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>109840</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>134004.8</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>2607188.01</v>
       </c>
     </row>
     <row r="14">
@@ -975,13 +1017,16 @@
         <v>27</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>109840</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>2965680</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>109840</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>134004.8</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>3618129.6</v>
       </c>
     </row>
     <row r="15">
@@ -1010,13 +1055,16 @@
         <v>4.557</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>109840</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>500540.88</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>109840</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>134004.8</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>610659.87</v>
       </c>
     </row>
     <row r="16">
@@ -1045,13 +1093,16 @@
         <v>10</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>109840</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>1098400</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>109840</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>134004.8</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1340048</v>
       </c>
     </row>
     <row r="17">
@@ -1080,13 +1131,16 @@
         <v>13.718</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>110000</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>1508980</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>110000</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>134200</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1840955.6</v>
       </c>
     </row>
     <row r="18">
@@ -1115,13 +1169,16 @@
         <v>0.3682</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>605000</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>222761</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>605000</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>738100</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>271768.42</v>
       </c>
     </row>
     <row r="19">
@@ -1150,13 +1207,16 @@
         <v>0.2</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>356000</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>1780000</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>2171600</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>434320</v>
       </c>
     </row>
     <row r="20">
@@ -1185,13 +1245,16 @@
         <v>3</v>
       </c>
       <c r="G20" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>390000</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>130000</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>158600</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>475800</v>
       </c>
     </row>
     <row r="21">
@@ -1220,13 +1283,16 @@
         <v>5</v>
       </c>
       <c r="G21" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>650000</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>130000</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>158600</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>793000</v>
       </c>
     </row>
     <row r="22">
@@ -1255,13 +1321,16 @@
         <v>1.9</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>228000</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>278160</v>
       </c>
     </row>
     <row r="23">
@@ -1290,13 +1359,16 @@
         <v>21.2</v>
       </c>
       <c r="G23" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>2544000</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>3103680</v>
       </c>
     </row>
     <row r="24">
@@ -1325,13 +1397,16 @@
         <v>1.2</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>144000</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>175680</v>
       </c>
     </row>
     <row r="25">
@@ -1360,13 +1435,16 @@
         <v>6.419</v>
       </c>
       <c r="G25" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>770280</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>939741.6</v>
       </c>
     </row>
     <row r="26">
@@ -1395,13 +1473,16 @@
         <v>2.3</v>
       </c>
       <c r="G26" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>276000</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>336720</v>
       </c>
     </row>
     <row r="27">
@@ -1430,13 +1511,16 @@
         <v>2.3</v>
       </c>
       <c r="G27" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>276000</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>336720</v>
       </c>
     </row>
     <row r="28">
@@ -1465,13 +1549,16 @@
         <v>7</v>
       </c>
       <c r="G28" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>840000</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>1024800</v>
       </c>
     </row>
     <row r="29">
@@ -1500,13 +1587,16 @@
         <v>2.5</v>
       </c>
       <c r="G29" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>300000</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>366000</v>
       </c>
     </row>
     <row r="30">
@@ -1535,13 +1625,16 @@
         <v>7.4</v>
       </c>
       <c r="G30" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>888000</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1083360</v>
       </c>
     </row>
     <row r="31">
@@ -1570,13 +1663,16 @@
         <v>7.4</v>
       </c>
       <c r="G31" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>888000</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>1083360</v>
       </c>
     </row>
     <row r="32">
@@ -1605,13 +1701,16 @@
         <v>2.28</v>
       </c>
       <c r="G32" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>273600</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>333792</v>
       </c>
     </row>
     <row r="33">
@@ -1640,13 +1739,16 @@
         <v>2.28</v>
       </c>
       <c r="G33" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>273600</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>333792</v>
       </c>
     </row>
     <row r="34">
@@ -1675,13 +1777,16 @@
         <v>0.8239</v>
       </c>
       <c r="G34" s="5" t="n">
+        <v>118890</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>97949.55</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>118890</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>145045.8</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>119498.45</v>
       </c>
     </row>
     <row r="35">
@@ -1710,13 +1815,16 @@
         <v>2.4463</v>
       </c>
       <c r="G35" s="5" t="n">
+        <v>119720</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>292876.78</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>119720</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>146058.4</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>357309.67</v>
       </c>
     </row>
     <row r="36">
@@ -1745,13 +1853,16 @@
         <v>1.4631</v>
       </c>
       <c r="G36" s="5" t="n">
+        <v>130200</v>
+      </c>
+      <c r="H36" s="5" t="n">
         <v>190492.23</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>130200</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>158844</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>232400.52</v>
       </c>
     </row>
     <row r="37">
@@ -1780,13 +1891,16 @@
         <v>0.9817</v>
       </c>
       <c r="G37" s="5" t="n">
+        <v>99950</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>98123.91</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>99950</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>121939</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>119711.17</v>
       </c>
     </row>
     <row r="38">
@@ -1815,13 +1929,16 @@
         <v>1.686</v>
       </c>
       <c r="G38" s="5" t="n">
+        <v>136200</v>
+      </c>
+      <c r="H38" s="5" t="n">
         <v>229633.2</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>136200</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>166164</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>280152.5</v>
       </c>
     </row>
     <row r="39">
@@ -1850,13 +1967,16 @@
         <v>1.44</v>
       </c>
       <c r="G39" s="5" t="n">
+        <v>142230</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>204810.06</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>142230</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>173520.6</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>249868.27</v>
       </c>
     </row>
     <row r="40">
@@ -1885,13 +2005,16 @@
         <v>1.44</v>
       </c>
       <c r="G40" s="5" t="n">
+        <v>120260</v>
+      </c>
+      <c r="H40" s="5" t="n">
         <v>173178.01</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>120260</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>146717.2</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>211277.17</v>
       </c>
     </row>
     <row r="41">
@@ -1920,13 +2043,16 @@
         <v>52.058</v>
       </c>
       <c r="G41" s="5" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>6767540</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>130000</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>158600</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>8256398.8</v>
       </c>
     </row>
     <row r="42">
@@ -1955,13 +2081,16 @@
         <v>7.181</v>
       </c>
       <c r="G42" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H42" s="5" t="n">
         <v>861720</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>1051298.4</v>
       </c>
     </row>
     <row r="43">
@@ -1990,13 +2119,16 @@
         <v>49.7889</v>
       </c>
       <c r="G43" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>5974665.6</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>7289092.03</v>
       </c>
     </row>
     <row r="44">
@@ -2025,13 +2157,16 @@
         <v>9.9558</v>
       </c>
       <c r="G44" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>1194700.8</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>1457534.98</v>
       </c>
     </row>
     <row r="45">
@@ -2060,13 +2195,16 @@
         <v>141.562</v>
       </c>
       <c r="G45" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>16987440</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>20724676.8</v>
       </c>
     </row>
     <row r="46">
@@ -2095,13 +2233,16 @@
         <v>56.8552</v>
       </c>
       <c r="G46" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H46" s="5" t="n">
         <v>6822624</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>8323601.28</v>
       </c>
     </row>
     <row r="47">
@@ -2130,13 +2271,16 @@
         <v>2.4</v>
       </c>
       <c r="G47" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>288000</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>351360</v>
       </c>
     </row>
     <row r="48">
@@ -2165,13 +2309,16 @@
         <v>23.76</v>
       </c>
       <c r="G48" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H48" s="5" t="n">
         <v>2851200</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>120000</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>146400</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>3478464</v>
       </c>
     </row>
     <row r="49">
@@ -2200,13 +2347,16 @@
         <v>5.52</v>
       </c>
       <c r="G49" s="5" t="n">
+        <v>99310</v>
+      </c>
+      <c r="H49" s="5" t="n">
         <v>548191.2</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>99310</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>121158.2</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>668793.26</v>
       </c>
     </row>
     <row r="50">
@@ -2235,13 +2385,16 @@
         <v>126.3551</v>
       </c>
       <c r="G50" s="5" t="n">
+        <v>99310</v>
+      </c>
+      <c r="H50" s="5" t="n">
         <v>12548329.95</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>99310</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>121158.2</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>15308962.54</v>
       </c>
     </row>
     <row r="51">
@@ -2270,13 +2423,16 @@
         <v>1.21</v>
       </c>
       <c r="G51" s="5" t="n">
+        <v>74140</v>
+      </c>
+      <c r="H51" s="5" t="n">
         <v>89709.39999999999</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>74140</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>90450.8</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>109445.47</v>
       </c>
     </row>
     <row r="52">
@@ -2305,13 +2461,16 @@
         <v>36.814</v>
       </c>
       <c r="G52" s="5" t="n">
+        <v>89320</v>
+      </c>
+      <c r="H52" s="5" t="n">
         <v>3288226.48</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>89320</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>108970.4</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>4011636.31</v>
       </c>
     </row>
     <row r="53">
@@ -2340,14 +2499,17 @@
         <v>130.609</v>
       </c>
       <c r="G53" s="5" t="n">
+        <v>103820</v>
+      </c>
+      <c r="H53" s="5" t="n">
         <v>13559826.38</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>103820</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>126660.4</v>
       </c>
+      <c r="J53" s="5" t="n">
+        <v>16542988.18</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -2359,7 +2521,16 @@
         <v>1017.1905</v>
       </c>
       <c r="G54" s="9" t="n">
+        <v>110996.49</v>
+      </c>
+      <c r="H54" s="9" t="n">
         <v>112904579.3</v>
+      </c>
+      <c r="I54" s="9" t="n">
+        <v>135415.72</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>137743586.75</v>
       </c>
     </row>
     <row r="55">
@@ -2368,7 +2539,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G55" s="9" t="n">
+      <c r="H55" s="9" t="n">
         <v>112904579.31215</v>
       </c>
     </row>
@@ -2378,7 +2549,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F56" s="9" t="n">
+      <c r="J56" s="9" t="n">
         <v>137743586.76</v>
       </c>
     </row>
